--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/GitHub/unitree-qmini-robot/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\okay1\Documents\GitHub\unitree-qmini-robot-components\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90392D3F-8468-1945-BDAF-396BFB4BC571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA3632D-7F8D-4115-8256-65FEF7A4967E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="500" windowWidth="45820" windowHeight="27260" activeTab="1" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
   </bookViews>
   <sheets>
     <sheet name="3D Print" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="195">
   <si>
     <t>Right Foot A</t>
   </si>
@@ -611,6 +609,22 @@
   </si>
   <si>
     <t>足端连接电机转轴</t>
+  </si>
+  <si>
+    <t>M5 x 8</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>FHCS 螺丝</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3 x 14 杯头</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>M3 螺母</t>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -618,13 +632,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0.00"/>
+    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -632,20 +646,20 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -653,62 +667,69 @@
       <b/>
       <sz val="16"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="4"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFC000"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -888,7 +909,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -900,7 +921,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -912,7 +933,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -924,7 +945,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -936,7 +957,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,7 +966,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,7 +981,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -987,13 +1008,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1011,6 +1032,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1020,13 +1044,10 @@
     <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1359,17 +1380,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE0F49-92DE-F34E-B54B-F98DD53080BB}">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="24" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="37.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="31.83203125" style="2" customWidth="1"/>
-    <col min="3" max="4" width="31.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1640625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="37.453125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="31.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1796875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="24" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>43</v>
@@ -1387,7 +1408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="24" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
@@ -1397,7 +1418,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="24" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1415,7 +1436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="24" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>48</v>
       </c>
@@ -1435,7 +1456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="24" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -1455,7 +1476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="24" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>53</v>
       </c>
@@ -1475,7 +1496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="24" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>23</v>
       </c>
@@ -1493,7 +1514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="24" customHeight="1">
       <c r="A8" s="22" t="s">
         <v>24</v>
       </c>
@@ -1505,7 +1526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="24" customHeight="1">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1521,7 +1542,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="24" customHeight="1">
       <c r="A10" s="22" t="s">
         <v>26</v>
       </c>
@@ -1537,7 +1558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="24" customHeight="1">
       <c r="A11" s="15" t="s">
         <v>27</v>
       </c>
@@ -1553,7 +1574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="24" customHeight="1">
       <c r="A12" s="15" t="s">
         <v>28</v>
       </c>
@@ -1571,7 +1592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="24" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12"/>
@@ -1581,7 +1602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="24" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12"/>
@@ -1591,7 +1612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="24" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12"/>
@@ -1601,7 +1622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="24" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12"/>
@@ -1611,7 +1632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="24" customHeight="1">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
@@ -1621,7 +1642,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="24" customHeight="1">
       <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
@@ -1637,7 +1658,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="24" customHeight="1">
       <c r="A19" s="15" t="s">
         <v>31</v>
       </c>
@@ -1653,7 +1674,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="24" customHeight="1">
       <c r="A20" s="15" t="s">
         <v>34</v>
       </c>
@@ -1669,7 +1690,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="24" customHeight="1">
       <c r="A21" s="15" t="s">
         <v>35</v>
       </c>
@@ -1685,7 +1706,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="24" customHeight="1">
       <c r="A22" s="15" t="s">
         <v>32</v>
       </c>
@@ -1705,7 +1726,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="24" customHeight="1">
       <c r="A23" s="15" t="s">
         <v>33</v>
       </c>
@@ -1725,7 +1746,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="24" customHeight="1">
       <c r="A24" s="15" t="s">
         <v>36</v>
       </c>
@@ -1745,7 +1766,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="24" customHeight="1">
       <c r="A25" s="15" t="s">
         <v>37</v>
       </c>
@@ -1765,7 +1786,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="24" customHeight="1">
       <c r="A26" s="6" t="s">
         <v>5</v>
       </c>
@@ -1775,7 +1796,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="24" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>6</v>
       </c>
@@ -1791,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="24" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>8</v>
       </c>
@@ -1807,7 +1828,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="24" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>9</v>
       </c>
@@ -1823,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="24" customHeight="1">
       <c r="A30" s="15" t="s">
         <v>10</v>
       </c>
@@ -1839,7 +1860,7 @@
         <v>126.89</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="24" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="12"/>
@@ -1847,7 +1868,7 @@
       <c r="E31" s="12"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="24" customHeight="1">
       <c r="A32" s="10" t="s">
         <v>15</v>
       </c>
@@ -1863,7 +1884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="24" customHeight="1">
       <c r="A33" s="10" t="s">
         <v>16</v>
       </c>
@@ -1879,7 +1900,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="24" customHeight="1">
       <c r="A34" s="15" t="s">
         <v>17</v>
       </c>
@@ -1895,7 +1916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="24" customHeight="1">
       <c r="A35" s="15" t="s">
         <v>18</v>
       </c>
@@ -1911,7 +1932,7 @@
         <v>126.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="24" customHeight="1">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -1921,7 +1942,7 @@
       <c r="E36" s="20"/>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="24" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>0</v>
       </c>
@@ -1939,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="24" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>1</v>
       </c>
@@ -1955,7 +1976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="24" customHeight="1">
       <c r="A39" s="15" t="s">
         <v>54</v>
       </c>
@@ -1971,7 +1992,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="24" customHeight="1">
       <c r="A40" s="10" t="s">
         <v>3</v>
       </c>
@@ -1989,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="24" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>4</v>
       </c>
@@ -2005,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="24" customHeight="1">
       <c r="A42" s="15" t="s">
         <v>55</v>
       </c>
@@ -2021,7 +2042,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="24" customHeight="1">
       <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
@@ -2031,7 +2052,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="24" customHeight="1">
       <c r="A44" s="22" t="s">
         <v>40</v>
       </c>
@@ -2051,7 +2072,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="24" customHeight="1">
       <c r="A45" s="22" t="s">
         <v>57</v>
       </c>
@@ -2069,7 +2090,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="24" customHeight="1">
       <c r="A46" s="22" t="s">
         <v>41</v>
       </c>
@@ -2085,7 +2106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="24" customHeight="1" thickBot="1">
       <c r="A47" s="26" t="s">
         <v>42</v>
       </c>
@@ -2101,7 +2122,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="58" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="58.05" customHeight="1" thickTop="1">
       <c r="A48" s="29"/>
       <c r="B48" s="30"/>
       <c r="C48" s="31"/>
@@ -2116,6 +2137,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2123,19 +2145,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33821E08-F46F-4446-B9C0-A0B043389FFA}">
   <dimension ref="A1:G60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="24" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
-    <col min="2" max="2" width="37.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="80.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="80.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.6328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="36" customWidth="1"/>
     <col min="7" max="7" width="19" style="44" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="2"/>
+    <col min="8" max="16384" width="10.81640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="35" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="37" t="s">
         <v>59</v>
       </c>
@@ -2158,18 +2180,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="50" t="s">
+    <row r="2" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1">
+      <c r="A2" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-    </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="53"/>
+    </row>
+    <row r="3" spans="1:7" ht="24" customHeight="1">
       <c r="A3" s="10" t="s">
         <v>176</v>
       </c>
@@ -2193,7 +2215,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="24" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>175</v>
       </c>
@@ -2217,7 +2239,7 @@
         <v>5.6000000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="24" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>174</v>
       </c>
@@ -2241,7 +2263,7 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="24" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>74</v>
       </c>
@@ -2263,7 +2285,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="24" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>84</v>
       </c>
@@ -2287,7 +2309,7 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="24" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>84</v>
       </c>
@@ -2309,7 +2331,7 @@
         <v>1.7999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="24" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>84</v>
       </c>
@@ -2333,7 +2355,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="24" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>90</v>
       </c>
@@ -2357,7 +2379,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="24" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>89</v>
       </c>
@@ -2381,7 +2403,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="24" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>89</v>
       </c>
@@ -2405,7 +2427,7 @@
         <v>5.3999999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="24" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>89</v>
       </c>
@@ -2429,7 +2451,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="24" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>89</v>
       </c>
@@ -2453,7 +2475,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="24" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>89</v>
       </c>
@@ -2477,7 +2499,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="24" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>89</v>
       </c>
@@ -2501,7 +2523,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="24" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>89</v>
       </c>
@@ -2525,7 +2547,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="24" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>110</v>
       </c>
@@ -2549,7 +2571,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="24" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>102</v>
       </c>
@@ -2573,7 +2595,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="24" customHeight="1">
       <c r="A20" s="10" t="s">
         <v>109</v>
       </c>
@@ -2597,7 +2619,7 @@
         <v>2.1240000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="24" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>109</v>
       </c>
@@ -2621,7 +2643,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="24" customHeight="1">
       <c r="A22" s="10" t="s">
         <v>141</v>
       </c>
@@ -2645,7 +2667,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="24" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>121</v>
       </c>
@@ -2669,7 +2691,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="24" customHeight="1">
       <c r="A24" s="10" t="s">
         <v>123</v>
       </c>
@@ -2691,7 +2713,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="24" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>126</v>
       </c>
@@ -2713,7 +2735,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="24" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>80</v>
       </c>
@@ -2735,7 +2757,7 @@
         <v>4485</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="24" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>158</v>
       </c>
@@ -2757,7 +2779,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="24" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>149</v>
       </c>
@@ -2779,7 +2801,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="24" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>152</v>
       </c>
@@ -2801,7 +2823,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="24" customHeight="1">
       <c r="A30" s="10" t="s">
         <v>154</v>
       </c>
@@ -2823,7 +2845,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="24" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>163</v>
       </c>
@@ -2845,18 +2867,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="50" t="s">
+    <row r="32" spans="1:7" ht="24" customHeight="1">
+      <c r="A32" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
-      <c r="E32" s="51"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="52"/>
-    </row>
-    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="53"/>
+    </row>
+    <row r="33" spans="1:7" ht="24" customHeight="1">
       <c r="A33" s="10" t="s">
         <v>84</v>
       </c>
@@ -2880,7 +2902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="24" customHeight="1">
       <c r="A34" s="10" t="s">
         <v>84</v>
       </c>
@@ -2904,7 +2926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="24" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>89</v>
       </c>
@@ -2928,7 +2950,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="24" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>124</v>
       </c>
@@ -2950,7 +2972,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="24" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>158</v>
       </c>
@@ -2972,7 +2994,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="24" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>80</v>
       </c>
@@ -2994,18 +3016,18 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="50" t="s">
+    <row r="39" spans="1:7" ht="24" customHeight="1">
+      <c r="A39" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="52"/>
-    </row>
-    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="53"/>
+    </row>
+    <row r="40" spans="1:7" ht="24" customHeight="1">
       <c r="A40" s="10" t="s">
         <v>174</v>
       </c>
@@ -3029,7 +3051,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="24" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>89</v>
       </c>
@@ -3051,14 +3073,14 @@
         <v>1.8599999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="31.2">
       <c r="A42" s="10" t="s">
         <v>189</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C42" s="53" t="s">
+      <c r="C42" s="50" t="s">
         <v>188</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -3075,7 +3097,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="24" customHeight="1">
       <c r="A43" s="10" t="s">
         <v>187</v>
       </c>
@@ -3095,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="24" customHeight="1">
       <c r="A44" s="45" t="s">
         <v>80</v>
       </c>
@@ -3117,18 +3139,18 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="50" t="s">
+    <row r="45" spans="1:7" ht="24" customHeight="1">
+      <c r="A45" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="52"/>
-    </row>
-    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="53"/>
+    </row>
+    <row r="46" spans="1:7" ht="24" customHeight="1">
       <c r="A46" s="10" t="s">
         <v>174</v>
       </c>
@@ -3152,7 +3174,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="24" customHeight="1">
       <c r="A47" s="10" t="s">
         <v>84</v>
       </c>
@@ -3176,7 +3198,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="24" customHeight="1">
       <c r="A48" s="10" t="s">
         <v>89</v>
       </c>
@@ -3200,7 +3222,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="24" customHeight="1">
       <c r="A49" s="10" t="s">
         <v>89</v>
       </c>
@@ -3224,18 +3246,18 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="50" t="s">
+    <row r="50" spans="1:7" ht="24" customHeight="1">
+      <c r="A50" s="51" t="s">
         <v>177</v>
       </c>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="52"/>
-    </row>
-    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="53"/>
+    </row>
+    <row r="51" spans="1:7" ht="24" customHeight="1">
       <c r="A51" s="10" t="s">
         <v>161</v>
       </c>
@@ -3253,18 +3275,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="50" t="s">
+    <row r="52" spans="1:7" ht="24" customHeight="1">
+      <c r="A52" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="52"/>
-    </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="53"/>
+    </row>
+    <row r="53" spans="1:7" ht="24" customHeight="1">
       <c r="A53" s="10" t="s">
         <v>170</v>
       </c>
@@ -3286,7 +3308,7 @@
         <v>65.95</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="24" customHeight="1">
       <c r="A54" s="10" t="s">
         <v>179</v>
       </c>
@@ -3310,43 +3332,59 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="10"/>
-      <c r="B55" s="10"/>
+    <row r="55" spans="1:7" ht="24" customHeight="1">
+      <c r="A55" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>191</v>
+      </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
-      <c r="E55" s="12"/>
+      <c r="E55" s="12">
+        <v>16</v>
+      </c>
       <c r="F55" s="40"/>
       <c r="G55" s="43">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="10"/>
-      <c r="B56" s="10"/>
+    <row r="56" spans="1:7" ht="24" customHeight="1">
+      <c r="A56" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>193</v>
+      </c>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
-      <c r="E56" s="12"/>
+      <c r="E56" s="12">
+        <v>8</v>
+      </c>
       <c r="F56" s="40"/>
       <c r="G56" s="43">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10"/>
+    <row r="57" spans="1:7" ht="24" customHeight="1">
+      <c r="A57" s="10" t="s">
+        <v>194</v>
+      </c>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
-      <c r="E57" s="12"/>
+      <c r="E57" s="12">
+        <v>8</v>
+      </c>
       <c r="F57" s="40"/>
       <c r="G57" s="43">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="24" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -3358,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="24" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -3370,7 +3408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="24" customHeight="1">
       <c r="G60" s="44">
         <f>SUM(G3:G59)</f>
         <v>13997.604000000003</v>
@@ -3385,6 +3423,7 @@
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A50:G50"/>
   </mergeCells>
+  <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{A478C749-2080-B344-A289-CDF5D97B29A2}"/>
     <hyperlink ref="C5" r:id="rId2" xr:uid="{44C7BED6-AA93-3C43-B7CD-0009ABF6B6BB}"/>
@@ -3431,5 +3470,6 @@
     <hyperlink ref="C54" r:id="rId43" xr:uid="{0925B719-C096-EE4D-83FA-1C819A974518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId44"/>
 </worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\okay1\Documents\GitHub\unitree-qmini-robot-components\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/GitHub/unitree-qmini-robot-components/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA3632D-7F8D-4115-8256-65FEF7A4967E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC07013-58E4-8142-9F94-8B0240F6BCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="27180" activeTab="2" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
   </bookViews>
   <sheets>
     <sheet name="3D Print" sheetId="1" r:id="rId1"/>
     <sheet name="BOM" sheetId="2" r:id="rId2"/>
+    <sheet name="Wiring" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="204">
   <si>
     <t>Right Foot A</t>
   </si>
@@ -625,6 +626,33 @@
   <si>
     <t>M3 螺母</t>
     <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>连接器</t>
+  </si>
+  <si>
+    <t>线径</t>
+  </si>
+  <si>
+    <t>长度</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>16 AWG</t>
+  </si>
+  <si>
+    <t>XT30(2+2)</t>
+  </si>
+  <si>
+    <t>连接</t>
+  </si>
+  <si>
+    <t>58cm</t>
+  </si>
+  <si>
+    <t>左电机 0 或右电机 0 连接至分电板</t>
   </si>
 </sst>
 </file>
@@ -632,13 +660,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -646,20 +674,22 @@
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -667,69 +697,88 @@
       <b/>
       <sz val="16"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="7" tint="0.39997558519241921"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="20"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="4"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFC000"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
+      <family val="4"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -883,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -909,7 +958,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -921,7 +970,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -933,7 +982,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -945,7 +994,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -957,7 +1006,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -966,7 +1015,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -981,7 +1030,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1008,13 +1057,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1035,6 +1084,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1046,8 +1098,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1380,17 +1432,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08BE0F49-92DE-F34E-B54B-F98DD53080BB}">
   <dimension ref="A1:F48"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="24" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.453125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" style="2" customWidth="1"/>
-    <col min="3" max="4" width="31.81640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.1796875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.81640625" style="1"/>
+    <col min="1" max="1" width="37.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" style="2" customWidth="1"/>
+    <col min="3" max="4" width="31.83203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3"/>
       <c r="B1" s="3" t="s">
         <v>43</v>
@@ -1408,7 +1460,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1">
+    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>19</v>
       </c>
@@ -1418,7 +1470,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1">
+    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1436,7 +1488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1">
+    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>48</v>
       </c>
@@ -1456,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1">
+    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>22</v>
       </c>
@@ -1476,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24" customHeight="1">
+    <row r="6" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>53</v>
       </c>
@@ -1496,7 +1548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="24" customHeight="1">
+    <row r="7" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>23</v>
       </c>
@@ -1514,7 +1566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1">
+    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
         <v>24</v>
       </c>
@@ -1526,7 +1578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24" customHeight="1">
+    <row r="9" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1542,7 +1594,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="24" customHeight="1">
+    <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="22" t="s">
         <v>26</v>
       </c>
@@ -1558,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="24" customHeight="1">
+    <row r="11" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>27</v>
       </c>
@@ -1574,7 +1626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="24" customHeight="1">
+    <row r="12" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>28</v>
       </c>
@@ -1592,7 +1644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="24" customHeight="1">
+    <row r="13" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="10"/>
       <c r="C13" s="12"/>
@@ -1602,7 +1654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="24" customHeight="1">
+    <row r="14" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="12"/>
@@ -1612,7 +1664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="24" customHeight="1">
+    <row r="15" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="10"/>
       <c r="C15" s="12"/>
@@ -1622,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="24" customHeight="1">
+    <row r="16" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="10"/>
       <c r="C16" s="12"/>
@@ -1632,7 +1684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="24" customHeight="1">
+    <row r="17" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
@@ -1642,7 +1694,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" ht="24" customHeight="1">
+    <row r="18" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>30</v>
       </c>
@@ -1658,7 +1710,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="24" customHeight="1">
+    <row r="19" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>31</v>
       </c>
@@ -1674,7 +1726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="24" customHeight="1">
+    <row r="20" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>34</v>
       </c>
@@ -1690,7 +1742,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="24" customHeight="1">
+    <row r="21" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>35</v>
       </c>
@@ -1706,7 +1758,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="24" customHeight="1">
+    <row r="22" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>32</v>
       </c>
@@ -1726,7 +1778,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="24" customHeight="1">
+    <row r="23" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>33</v>
       </c>
@@ -1746,7 +1798,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="24" customHeight="1">
+    <row r="24" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
         <v>36</v>
       </c>
@@ -1766,7 +1818,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="24" customHeight="1">
+    <row r="25" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
         <v>37</v>
       </c>
@@ -1786,7 +1838,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1">
+    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
         <v>5</v>
       </c>
@@ -1796,7 +1848,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1">
+    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>6</v>
       </c>
@@ -1812,7 +1864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="24" customHeight="1">
+    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>8</v>
       </c>
@@ -1828,7 +1880,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24" customHeight="1">
+    <row r="29" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>9</v>
       </c>
@@ -1844,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="24" customHeight="1">
+    <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>10</v>
       </c>
@@ -1860,7 +1912,7 @@
         <v>126.89</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24" customHeight="1">
+    <row r="31" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
       <c r="C31" s="12"/>
@@ -1868,7 +1920,7 @@
       <c r="E31" s="12"/>
       <c r="F31" s="13"/>
     </row>
-    <row r="32" spans="1:6" ht="24" customHeight="1">
+    <row r="32" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
         <v>15</v>
       </c>
@@ -1884,7 +1936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="24" customHeight="1">
+    <row r="33" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>16</v>
       </c>
@@ -1900,7 +1952,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="24" customHeight="1">
+    <row r="34" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>17</v>
       </c>
@@ -1916,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="24" customHeight="1">
+    <row r="35" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>18</v>
       </c>
@@ -1932,7 +1984,7 @@
         <v>126.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="24" customHeight="1">
+    <row r="36" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -1942,7 +1994,7 @@
       <c r="E36" s="20"/>
       <c r="F36" s="21"/>
     </row>
-    <row r="37" spans="1:6" ht="24" customHeight="1">
+    <row r="37" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +2012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="24" customHeight="1">
+    <row r="38" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
         <v>1</v>
       </c>
@@ -1976,7 +2028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="24" customHeight="1">
+    <row r="39" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>54</v>
       </c>
@@ -1992,7 +2044,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24" customHeight="1">
+    <row r="40" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>3</v>
       </c>
@@ -2010,7 +2062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="24" customHeight="1">
+    <row r="41" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>4</v>
       </c>
@@ -2026,7 +2078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="24" customHeight="1">
+    <row r="42" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>55</v>
       </c>
@@ -2042,7 +2094,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="24" customHeight="1">
+    <row r="43" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
@@ -2052,7 +2104,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" ht="24" customHeight="1">
+    <row r="44" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="22" t="s">
         <v>40</v>
       </c>
@@ -2072,7 +2124,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="24" customHeight="1">
+    <row r="45" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="22" t="s">
         <v>57</v>
       </c>
@@ -2090,7 +2142,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="24" customHeight="1">
+    <row r="46" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="22" t="s">
         <v>41</v>
       </c>
@@ -2106,7 +2158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="24" customHeight="1" thickBot="1">
+    <row r="47" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
         <v>42</v>
       </c>
@@ -2122,7 +2174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="58.05" customHeight="1" thickTop="1">
+    <row r="48" spans="1:6" ht="58" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A48" s="29"/>
       <c r="B48" s="30"/>
       <c r="C48" s="31"/>
@@ -2145,19 +2197,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33821E08-F46F-4446-B9C0-A0B043389FFA}">
   <dimension ref="A1:G60"/>
-  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="24" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
-    <col min="2" max="2" width="37.6328125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="80.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="64.6328125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="80.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="64.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="36" customWidth="1"/>
     <col min="7" max="7" width="19" style="44" customWidth="1"/>
-    <col min="8" max="16384" width="10.81640625" style="2"/>
+    <col min="8" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="35" customFormat="1" ht="24" customHeight="1">
+    <row r="1" spans="1:7" s="35" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="37" t="s">
         <v>59</v>
       </c>
@@ -2180,18 +2232,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1">
-      <c r="A2" s="51" t="s">
+    <row r="2" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="53"/>
-    </row>
-    <row r="3" spans="1:7" ht="24" customHeight="1">
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="54"/>
+    </row>
+    <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>176</v>
       </c>
@@ -2215,7 +2267,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1">
+    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>175</v>
       </c>
@@ -2239,7 +2291,7 @@
         <v>5.6000000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="24" customHeight="1">
+    <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>174</v>
       </c>
@@ -2263,7 +2315,7 @@
         <v>2.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24" customHeight="1">
+    <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>74</v>
       </c>
@@ -2285,7 +2337,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24" customHeight="1">
+    <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>84</v>
       </c>
@@ -2309,7 +2361,7 @@
         <v>7.1999999999999993</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="24" customHeight="1">
+    <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
         <v>84</v>
       </c>
@@ -2331,7 +2383,7 @@
         <v>1.7999999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="24" customHeight="1">
+    <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>84</v>
       </c>
@@ -2355,7 +2407,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24" customHeight="1">
+    <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>90</v>
       </c>
@@ -2379,7 +2431,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24" customHeight="1">
+    <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>89</v>
       </c>
@@ -2403,7 +2455,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24" customHeight="1">
+    <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>89</v>
       </c>
@@ -2427,7 +2479,7 @@
         <v>5.3999999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24" customHeight="1">
+    <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>89</v>
       </c>
@@ -2451,7 +2503,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="24" customHeight="1">
+    <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
         <v>89</v>
       </c>
@@ -2475,7 +2527,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24" customHeight="1">
+    <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>89</v>
       </c>
@@ -2499,7 +2551,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24" customHeight="1">
+    <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
         <v>89</v>
       </c>
@@ -2523,7 +2575,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="24" customHeight="1">
+    <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>89</v>
       </c>
@@ -2547,7 +2599,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1">
+    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
         <v>110</v>
       </c>
@@ -2571,7 +2623,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1">
+    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>102</v>
       </c>
@@ -2595,7 +2647,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1">
+    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
         <v>109</v>
       </c>
@@ -2619,7 +2671,7 @@
         <v>2.1240000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1">
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>109</v>
       </c>
@@ -2643,7 +2695,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1">
+    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="10" t="s">
         <v>141</v>
       </c>
@@ -2667,7 +2719,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="24" customHeight="1">
+    <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>121</v>
       </c>
@@ -2691,7 +2743,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1">
+    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10" t="s">
         <v>123</v>
       </c>
@@ -2713,7 +2765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24" customHeight="1">
+    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>126</v>
       </c>
@@ -2735,7 +2787,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1">
+    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="10" t="s">
         <v>80</v>
       </c>
@@ -2757,7 +2809,7 @@
         <v>4485</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="24" customHeight="1">
+    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>158</v>
       </c>
@@ -2779,7 +2831,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="24" customHeight="1">
+    <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
         <v>149</v>
       </c>
@@ -2801,7 +2853,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="24" customHeight="1">
+    <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>152</v>
       </c>
@@ -2823,7 +2875,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="24" customHeight="1">
+    <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
         <v>154</v>
       </c>
@@ -2845,7 +2897,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24" customHeight="1">
+    <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>163</v>
       </c>
@@ -2867,18 +2919,18 @@
         <v>265</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1">
-      <c r="A32" s="51" t="s">
+    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="53"/>
-    </row>
-    <row r="33" spans="1:7" ht="24" customHeight="1">
+      <c r="B32" s="53"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="54"/>
+    </row>
+    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>84</v>
       </c>
@@ -2902,7 +2954,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="24" customHeight="1">
+    <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>84</v>
       </c>
@@ -2926,7 +2978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="24" customHeight="1">
+    <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>89</v>
       </c>
@@ -2950,7 +3002,7 @@
         <v>4.32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="24" customHeight="1">
+    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
         <v>124</v>
       </c>
@@ -2972,7 +3024,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="24" customHeight="1">
+    <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>158</v>
       </c>
@@ -2994,7 +3046,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24" customHeight="1">
+    <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
         <v>80</v>
       </c>
@@ -3016,18 +3068,18 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="24" customHeight="1">
-      <c r="A39" s="51" t="s">
+    <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="52" t="s">
         <v>183</v>
       </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="53"/>
-    </row>
-    <row r="40" spans="1:7" ht="24" customHeight="1">
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="54"/>
+    </row>
+    <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
         <v>174</v>
       </c>
@@ -3051,7 +3103,7 @@
         <v>1.2000000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="24" customHeight="1">
+    <row r="41" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>89</v>
       </c>
@@ -3073,7 +3125,7 @@
         <v>1.8599999999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="31.2">
+    <row r="42" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A42" s="10" t="s">
         <v>189</v>
       </c>
@@ -3097,7 +3149,7 @@
         <v>3.5999999999999996</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="24" customHeight="1">
+    <row r="43" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>187</v>
       </c>
@@ -3117,7 +3169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24" customHeight="1">
+    <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="45" t="s">
         <v>80</v>
       </c>
@@ -3139,18 +3191,18 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="24" customHeight="1">
-      <c r="A45" s="51" t="s">
+    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="52"/>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="53"/>
-    </row>
-    <row r="46" spans="1:7" ht="24" customHeight="1">
+      <c r="B45" s="53"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="53"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="54"/>
+    </row>
+    <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
         <v>174</v>
       </c>
@@ -3174,7 +3226,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="24" customHeight="1">
+    <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>84</v>
       </c>
@@ -3198,7 +3250,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24" customHeight="1">
+    <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
         <v>89</v>
       </c>
@@ -3222,7 +3274,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24" customHeight="1">
+    <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
         <v>89</v>
       </c>
@@ -3246,18 +3298,18 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="24" customHeight="1">
-      <c r="A50" s="51" t="s">
+    <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="53"/>
-    </row>
-    <row r="51" spans="1:7" ht="24" customHeight="1">
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="54"/>
+    </row>
+    <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
         <v>161</v>
       </c>
@@ -3275,18 +3327,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="24" customHeight="1">
-      <c r="A52" s="51" t="s">
+    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="B52" s="52"/>
-      <c r="C52" s="52"/>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="53"/>
-    </row>
-    <row r="53" spans="1:7" ht="24" customHeight="1">
+      <c r="B52" s="53"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="54"/>
+    </row>
+    <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>170</v>
       </c>
@@ -3308,7 +3360,7 @@
         <v>65.95</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="24" customHeight="1">
+    <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
         <v>179</v>
       </c>
@@ -3332,7 +3384,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="24" customHeight="1">
+    <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
         <v>179</v>
       </c>
@@ -3350,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="24" customHeight="1">
+    <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
         <v>192</v>
       </c>
@@ -3368,7 +3420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="24" customHeight="1">
+    <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
         <v>194</v>
       </c>
@@ -3384,7 +3436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="24" customHeight="1">
+    <row r="58" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="10"/>
       <c r="B58" s="10"/>
       <c r="C58" s="10"/>
@@ -3396,7 +3448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="24" customHeight="1">
+    <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="10"/>
       <c r="B59" s="10"/>
       <c r="C59" s="10"/>
@@ -3408,7 +3460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24" customHeight="1">
+    <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G60" s="44">
         <f>SUM(G3:G59)</f>
         <v>13997.604000000003</v>
@@ -3472,4 +3524,53 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId44"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1191EA9B-6AFA-D44D-9833-D84114EDB3BD}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="23.5" customWidth="1"/>
+    <col min="3" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="38.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="B1" s="51" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1" s="51" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="51" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/GitHub/unitree-qmini-robot-components/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC07013-58E4-8142-9F94-8B0240F6BCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723BF0D-7BE6-E54C-B679-C445F7B2B582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="27180" activeTab="2" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="210">
   <si>
     <t>Right Foot A</t>
   </si>
@@ -653,6 +653,24 @@
   </si>
   <si>
     <t>左电机 0 或右电机 0 连接至分电板</t>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?id=593581996419&amp;skuId=4189077672129</t>
+  </si>
+  <si>
+    <t>M3 x 4 OD 5</t>
+  </si>
+  <si>
+    <t>大腿</t>
+  </si>
+  <si>
+    <t>小腿</t>
+  </si>
+  <si>
+    <t>25cm</t>
+  </si>
+  <si>
+    <t>左电机 1 或右电机 1 连接至左电机 2 或右电机 2</t>
   </si>
 </sst>
 </file>
@@ -932,7 +950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1095,6 +1113,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2296,10 +2323,10 @@
         <v>174</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>72</v>
@@ -2333,7 +2360,7 @@
         <v>1.42</v>
       </c>
       <c r="G6" s="43">
-        <f t="shared" si="0"/>
+        <f>E6*F6</f>
         <v>2.84</v>
       </c>
     </row>
@@ -3478,62 +3505,62 @@
   <phoneticPr fontId="13" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{A478C749-2080-B344-A289-CDF5D97B29A2}"/>
-    <hyperlink ref="C5" r:id="rId2" xr:uid="{44C7BED6-AA93-3C43-B7CD-0009ABF6B6BB}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{B2AA866E-24F3-1646-ACED-D65EF9988155}"/>
-    <hyperlink ref="C40" r:id="rId4" xr:uid="{5010F871-A4EB-C348-B9FA-9AFAB7A4795F}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{6D0F970B-33A6-5741-B59A-13BE191765B5}"/>
-    <hyperlink ref="C46" r:id="rId6" xr:uid="{6E9AF94B-6606-EF47-BF3F-E19A5CFAFBEA}"/>
-    <hyperlink ref="C7" r:id="rId7" xr:uid="{D08990E8-0BCD-A44E-8FA8-5BE704D9FBEC}"/>
-    <hyperlink ref="C9" r:id="rId8" xr:uid="{E2E6BF14-5F83-F745-A590-905519EB4A90}"/>
-    <hyperlink ref="C10" r:id="rId9" xr:uid="{53620724-76B4-204B-AE5B-48ED373D3F0E}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{3751F033-84A3-2049-9763-EEFF4D133951}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{5C479939-3F8D-3446-86C5-81A48446719D}"/>
-    <hyperlink ref="C17" r:id="rId12" xr:uid="{47964371-1F96-6147-B384-4A7FCC0FB339}"/>
-    <hyperlink ref="C19" r:id="rId13" xr:uid="{0D761B1C-BFCE-CA4C-AC56-8959BBCD1D8C}"/>
-    <hyperlink ref="C14" r:id="rId14" xr:uid="{C2BA66AB-51D1-4E48-BDF6-5786EE1F2757}"/>
-    <hyperlink ref="C12" r:id="rId15" xr:uid="{5A619F16-5DF6-7A47-930C-607E13BD2744}"/>
-    <hyperlink ref="C20" r:id="rId16" xr:uid="{63E6DFF5-E6E6-9D48-BEF0-976C1610D4CA}"/>
-    <hyperlink ref="C18" r:id="rId17" xr:uid="{33FB920F-0669-0043-8C0C-BC6FBFCB38E1}"/>
-    <hyperlink ref="C15" r:id="rId18" xr:uid="{E3D98391-497D-E645-A06E-B9C450FAA734}"/>
-    <hyperlink ref="C16" r:id="rId19" xr:uid="{A82B3F0C-F6F0-BA48-95E6-EDBA66CD97B8}"/>
-    <hyperlink ref="C33" r:id="rId20" xr:uid="{D95FFA29-399D-6745-AC54-EDBAF115DD55}"/>
-    <hyperlink ref="C35" r:id="rId21" xr:uid="{DE78C3B5-25F3-B54C-AF32-A45A3CCF82C6}"/>
-    <hyperlink ref="C25" r:id="rId22" xr:uid="{E5990545-4A5C-BF4D-A2E3-33113701B5BE}"/>
-    <hyperlink ref="C26" r:id="rId23" xr:uid="{D97E6BC1-9B0F-7E4B-8DD8-6831F4863D0B}"/>
-    <hyperlink ref="C38" r:id="rId24" xr:uid="{52B47181-A334-734F-89EA-4D3CC6EE8FEE}"/>
-    <hyperlink ref="C44" r:id="rId25" xr:uid="{9DED03EC-6FA0-E340-9F64-4A2AFDB1BB32}"/>
-    <hyperlink ref="C34" r:id="rId26" xr:uid="{1B940CD5-6B42-114A-91F4-C00313929BF7}"/>
-    <hyperlink ref="C36" r:id="rId27" xr:uid="{9BF33B54-D294-6A41-BBDB-50238FA80D2D}"/>
-    <hyperlink ref="C42" r:id="rId28" display="https://item.taobao.com/item.htm?id=537967383377&amp;skuId=5461813862733" xr:uid="{F14BE297-86D6-B04A-98BE-ECD2D9A15FD8}"/>
-    <hyperlink ref="C21" r:id="rId29" xr:uid="{A0566B4B-F7CD-C14A-9EBE-943CA43F653D}"/>
-    <hyperlink ref="C22" r:id="rId30" xr:uid="{4BBCC18B-64B9-3948-8B17-249473C5AF6C}"/>
-    <hyperlink ref="C48" r:id="rId31" xr:uid="{AFDE7C59-FB6E-0B4D-A90B-C615F01A2424}"/>
-    <hyperlink ref="C47" r:id="rId32" xr:uid="{7295D0B3-C7AB-5D42-9A78-48C8E9745CA1}"/>
-    <hyperlink ref="C49" r:id="rId33" xr:uid="{0CFFB14A-47E8-B945-BCEB-B671BA1D6F52}"/>
-    <hyperlink ref="C28" r:id="rId34" xr:uid="{6A187383-C123-564D-BC92-969FA3FB5726}"/>
-    <hyperlink ref="C24" r:id="rId35" xr:uid="{1A29D440-BF31-E94C-BCA6-0C1202A21991}"/>
-    <hyperlink ref="C29" r:id="rId36" xr:uid="{36344359-AB27-274E-A2FC-98CD85B6FB8C}"/>
-    <hyperlink ref="C30" r:id="rId37" xr:uid="{A971E1C7-2D55-DA4F-9835-BC42C1DB56AF}"/>
-    <hyperlink ref="C37" r:id="rId38" xr:uid="{902445E2-BD52-B240-B54D-20CF95DAB079}"/>
-    <hyperlink ref="C27" r:id="rId39" xr:uid="{D0310BD2-7368-3C4A-AB34-40C7279D4F0B}"/>
-    <hyperlink ref="C31" r:id="rId40" xr:uid="{FAD92DE1-A270-F24C-8E9F-F880408C8288}"/>
-    <hyperlink ref="C23" r:id="rId41" xr:uid="{3E7B7CBC-84DD-1241-A9BD-85A9EBC5992B}"/>
-    <hyperlink ref="C53" r:id="rId42" xr:uid="{164D90D5-3E91-3245-93D1-4C111CB2C8F2}"/>
-    <hyperlink ref="C54" r:id="rId43" xr:uid="{0925B719-C096-EE4D-83FA-1C819A974518}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{B2AA866E-24F3-1646-ACED-D65EF9988155}"/>
+    <hyperlink ref="C40" r:id="rId3" xr:uid="{5010F871-A4EB-C348-B9FA-9AFAB7A4795F}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{6D0F970B-33A6-5741-B59A-13BE191765B5}"/>
+    <hyperlink ref="C46" r:id="rId5" xr:uid="{6E9AF94B-6606-EF47-BF3F-E19A5CFAFBEA}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{D08990E8-0BCD-A44E-8FA8-5BE704D9FBEC}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{E2E6BF14-5F83-F745-A590-905519EB4A90}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{53620724-76B4-204B-AE5B-48ED373D3F0E}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{3751F033-84A3-2049-9763-EEFF4D133951}"/>
+    <hyperlink ref="C13" r:id="rId10" xr:uid="{5C479939-3F8D-3446-86C5-81A48446719D}"/>
+    <hyperlink ref="C17" r:id="rId11" xr:uid="{47964371-1F96-6147-B384-4A7FCC0FB339}"/>
+    <hyperlink ref="C19" r:id="rId12" xr:uid="{0D761B1C-BFCE-CA4C-AC56-8959BBCD1D8C}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{C2BA66AB-51D1-4E48-BDF6-5786EE1F2757}"/>
+    <hyperlink ref="C12" r:id="rId14" xr:uid="{5A619F16-5DF6-7A47-930C-607E13BD2744}"/>
+    <hyperlink ref="C20" r:id="rId15" xr:uid="{63E6DFF5-E6E6-9D48-BEF0-976C1610D4CA}"/>
+    <hyperlink ref="C18" r:id="rId16" xr:uid="{33FB920F-0669-0043-8C0C-BC6FBFCB38E1}"/>
+    <hyperlink ref="C15" r:id="rId17" xr:uid="{E3D98391-497D-E645-A06E-B9C450FAA734}"/>
+    <hyperlink ref="C16" r:id="rId18" xr:uid="{A82B3F0C-F6F0-BA48-95E6-EDBA66CD97B8}"/>
+    <hyperlink ref="C33" r:id="rId19" xr:uid="{D95FFA29-399D-6745-AC54-EDBAF115DD55}"/>
+    <hyperlink ref="C35" r:id="rId20" xr:uid="{DE78C3B5-25F3-B54C-AF32-A45A3CCF82C6}"/>
+    <hyperlink ref="C25" r:id="rId21" xr:uid="{E5990545-4A5C-BF4D-A2E3-33113701B5BE}"/>
+    <hyperlink ref="C26" r:id="rId22" xr:uid="{D97E6BC1-9B0F-7E4B-8DD8-6831F4863D0B}"/>
+    <hyperlink ref="C38" r:id="rId23" xr:uid="{52B47181-A334-734F-89EA-4D3CC6EE8FEE}"/>
+    <hyperlink ref="C44" r:id="rId24" xr:uid="{9DED03EC-6FA0-E340-9F64-4A2AFDB1BB32}"/>
+    <hyperlink ref="C34" r:id="rId25" xr:uid="{1B940CD5-6B42-114A-91F4-C00313929BF7}"/>
+    <hyperlink ref="C36" r:id="rId26" xr:uid="{9BF33B54-D294-6A41-BBDB-50238FA80D2D}"/>
+    <hyperlink ref="C42" r:id="rId27" display="https://item.taobao.com/item.htm?id=537967383377&amp;skuId=5461813862733" xr:uid="{F14BE297-86D6-B04A-98BE-ECD2D9A15FD8}"/>
+    <hyperlink ref="C21" r:id="rId28" xr:uid="{A0566B4B-F7CD-C14A-9EBE-943CA43F653D}"/>
+    <hyperlink ref="C22" r:id="rId29" xr:uid="{4BBCC18B-64B9-3948-8B17-249473C5AF6C}"/>
+    <hyperlink ref="C48" r:id="rId30" xr:uid="{AFDE7C59-FB6E-0B4D-A90B-C615F01A2424}"/>
+    <hyperlink ref="C47" r:id="rId31" xr:uid="{7295D0B3-C7AB-5D42-9A78-48C8E9745CA1}"/>
+    <hyperlink ref="C49" r:id="rId32" xr:uid="{0CFFB14A-47E8-B945-BCEB-B671BA1D6F52}"/>
+    <hyperlink ref="C28" r:id="rId33" xr:uid="{6A187383-C123-564D-BC92-969FA3FB5726}"/>
+    <hyperlink ref="C24" r:id="rId34" xr:uid="{1A29D440-BF31-E94C-BCA6-0C1202A21991}"/>
+    <hyperlink ref="C29" r:id="rId35" xr:uid="{36344359-AB27-274E-A2FC-98CD85B6FB8C}"/>
+    <hyperlink ref="C30" r:id="rId36" xr:uid="{A971E1C7-2D55-DA4F-9835-BC42C1DB56AF}"/>
+    <hyperlink ref="C37" r:id="rId37" xr:uid="{902445E2-BD52-B240-B54D-20CF95DAB079}"/>
+    <hyperlink ref="C27" r:id="rId38" xr:uid="{D0310BD2-7368-3C4A-AB34-40C7279D4F0B}"/>
+    <hyperlink ref="C31" r:id="rId39" xr:uid="{FAD92DE1-A270-F24C-8E9F-F880408C8288}"/>
+    <hyperlink ref="C23" r:id="rId40" xr:uid="{3E7B7CBC-84DD-1241-A9BD-85A9EBC5992B}"/>
+    <hyperlink ref="C53" r:id="rId41" xr:uid="{164D90D5-3E91-3245-93D1-4C111CB2C8F2}"/>
+    <hyperlink ref="C54" r:id="rId42" xr:uid="{0925B719-C096-EE4D-83FA-1C819A974518}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId44"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId43"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1191EA9B-6AFA-D44D-9833-D84114EDB3BD}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="23.5" customWidth="1"/>
-    <col min="3" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="38.33203125" customWidth="1"/>
+    <col min="1" max="2" width="23.5" style="55" customWidth="1"/>
+    <col min="3" max="3" width="24" style="55" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="52.83203125" style="57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -3549,13 +3576,13 @@
       <c r="D1" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="56" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>206</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>199</v>
@@ -3566,8 +3593,25 @@
       <c r="D2" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>203</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="55" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/BOM.xlsx
+++ b/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tony/Documents/GitHub/unitree-qmini-robot-components/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723BF0D-7BE6-E54C-B679-C445F7B2B582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1BBC07-CB9A-6A4C-9B25-FAF9E0AB19C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="27180" activeTab="2" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="27180" activeTab="1" xr2:uid="{AB9389B4-2FA2-4848-9210-F8543C78B964}"/>
   </bookViews>
   <sheets>
     <sheet name="3D Print" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="210">
   <si>
     <t>Right Foot A</t>
   </si>
@@ -613,19 +613,19 @@
   </si>
   <si>
     <t>M5 x 8</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>FHCS 螺丝</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>M3 x 14 杯头</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>M3 螺母</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>连接器</t>
@@ -680,7 +680,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -774,13 +774,6 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -950,7 +943,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1084,26 +1077,20 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1113,15 +1100,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2216,14 +2194,14 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33821E08-F46F-4446-B9C0-A0B043389FFA}">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="30" style="2" customWidth="1"/>
@@ -2260,154 +2238,141 @@
       </c>
     </row>
     <row r="2" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
     </row>
     <row r="3" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C3" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>78</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="D3" s="10"/>
       <c r="E3" s="12">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F3" s="40">
-        <v>0.15</v>
+        <v>550</v>
       </c>
       <c r="G3" s="43">
         <f>E3*F3</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" s="12">
-        <v>28</v>
-      </c>
-      <c r="F4" s="40">
-        <v>0.2</v>
-      </c>
-      <c r="G4" s="43">
-        <f>E4*F4</f>
-        <v>5.6000000000000005</v>
-      </c>
+        <v>6050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="34" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="52"/>
     </row>
     <row r="5" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>205</v>
+        <v>61</v>
       </c>
       <c r="C5" s="41" t="s">
-        <v>204</v>
+        <v>71</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E5" s="12">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5" s="40">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G5" s="43">
-        <f t="shared" ref="G5:G40" si="0">E5*F5</f>
-        <v>2.4000000000000004</v>
+        <f>E5*F5</f>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="10"/>
+        <v>68</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>77</v>
+      </c>
       <c r="E6" s="12">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="F6" s="40">
-        <v>1.42</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="43">
         <f>E6*F6</f>
-        <v>2.84</v>
+        <v>5.6000000000000005</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="C7" s="41" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
       <c r="E7" s="12">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F7" s="40">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="43">
-        <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <f t="shared" ref="G7:G40" si="0">E7*F7</f>
+        <v>2.4000000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="10" t="s">
-        <v>173</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="10"/>
       <c r="E8" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F8" s="40">
-        <v>0.3</v>
+        <v>1.42</v>
       </c>
       <c r="G8" s="43">
         <f>E8*F8</f>
-        <v>1.7999999999999998</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2415,95 +2380,93 @@
         <v>84</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="E9" s="12">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F9" s="40">
         <v>0.3</v>
       </c>
       <c r="G9" s="43">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>7.1999999999999993</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>92</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="C10" s="41"/>
       <c r="D10" s="10" t="s">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="E10" s="12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F10" s="40">
         <v>0.3</v>
       </c>
       <c r="G10" s="43">
-        <f t="shared" ref="G10" si="1">E10*F10</f>
-        <v>3.5999999999999996</v>
+        <f>E10*F10</f>
+        <v>1.7999999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C11" s="41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E11" s="12">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F11" s="40">
         <v>0.3</v>
       </c>
       <c r="G11" s="43">
-        <f t="shared" ref="G11:G12" si="2">E11*F11</f>
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="C12" s="41" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="E12" s="12">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F12" s="40">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="G12" s="43">
-        <f t="shared" si="2"/>
-        <v>5.3999999999999995</v>
+        <f t="shared" ref="G12" si="1">E12*F12</f>
+        <v>3.5999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2511,10 +2474,10 @@
         <v>89</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>95</v>
@@ -2523,11 +2486,11 @@
         <v>4</v>
       </c>
       <c r="F13" s="40">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="G13" s="43">
-        <f t="shared" ref="G13:G16" si="3">E13*F13</f>
-        <v>1.44</v>
+        <f t="shared" ref="G13:G14" si="2">E13*F13</f>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2535,23 +2498,23 @@
         <v>89</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C14" s="41" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E14" s="12">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F14" s="40">
         <v>0.36</v>
       </c>
       <c r="G14" s="43">
-        <f t="shared" si="3"/>
-        <v>2.16</v>
+        <f t="shared" si="2"/>
+        <v>5.3999999999999995</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2559,23 +2522,23 @@
         <v>89</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="C15" s="41" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="E15" s="12">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F15" s="40">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="G15" s="43">
-        <f t="shared" si="3"/>
-        <v>4.32</v>
+        <f t="shared" ref="G15:G18" si="3">E15*F15</f>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2583,23 +2546,23 @@
         <v>89</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="C16" s="41" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="E16" s="12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" s="40">
-        <v>0.28000000000000003</v>
+        <v>0.36</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="3"/>
-        <v>1.1200000000000001</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -2607,392 +2570,394 @@
         <v>89</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="12">
+        <v>9</v>
+      </c>
+      <c r="F17" s="40">
+        <v>0.48</v>
+      </c>
+      <c r="G17" s="43">
+        <f t="shared" si="3"/>
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="12">
+        <v>4</v>
+      </c>
+      <c r="F18" s="40">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G18" s="43">
+        <f t="shared" si="3"/>
+        <v>1.1200000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C19" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E19" s="12">
         <v>4</v>
       </c>
-      <c r="F17" s="40">
+      <c r="F19" s="40">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G17" s="43">
+      <c r="G19" s="43">
         <f t="shared" si="0"/>
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B20" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C20" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E20" s="12">
         <v>2</v>
       </c>
-      <c r="F18" s="40">
+      <c r="F20" s="40">
         <v>3</v>
       </c>
-      <c r="G18" s="43">
+      <c r="G20" s="43">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B21" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C21" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D21" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E19" s="12">
+      <c r="E21" s="12">
         <v>4</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F21" s="40">
         <v>6.5</v>
       </c>
-      <c r="G19" s="43">
+      <c r="G21" s="43">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
+    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B22" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C22" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E22" s="12">
         <v>2</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F22" s="40">
         <v>1.0620000000000001</v>
       </c>
-      <c r="G20" s="43">
+      <c r="G22" s="43">
         <f t="shared" si="0"/>
         <v>2.1240000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="12">
-        <v>2</v>
-      </c>
-      <c r="F21" s="40">
-        <v>1.585</v>
-      </c>
-      <c r="G21" s="43">
-        <f t="shared" ref="G21" si="4">E21*F21</f>
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C22" s="41" t="s">
-        <v>142</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="E22" s="12">
-        <v>2</v>
-      </c>
-      <c r="F22" s="40">
-        <v>0.46</v>
-      </c>
-      <c r="G22" s="43">
-        <f t="shared" ref="G22" si="5">E22*F22</f>
-        <v>0.92</v>
-      </c>
-    </row>
     <row r="23" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="12">
+        <v>2</v>
+      </c>
+      <c r="F23" s="40">
+        <v>1.585</v>
+      </c>
+      <c r="G23" s="43">
+        <f t="shared" ref="G23" si="4">E23*F23</f>
+        <v>3.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="12">
+        <v>2</v>
+      </c>
+      <c r="F24" s="40">
+        <v>0.46</v>
+      </c>
+      <c r="G24" s="43">
+        <f t="shared" ref="G24" si="5">E24*F24</f>
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B25" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C25" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D25" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E25" s="12">
         <v>1</v>
       </c>
-      <c r="F23" s="40">
+      <c r="F25" s="40">
         <v>1.1200000000000001</v>
       </c>
-      <c r="G23" s="43">
+      <c r="G25" s="43">
         <f t="shared" si="0"/>
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
+    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B26" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C26" s="41" t="s">
         <v>151</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="12">
+      <c r="D26" s="10"/>
+      <c r="E26" s="12">
         <v>2</v>
       </c>
-      <c r="F24" s="40">
+      <c r="F26" s="40">
         <v>8</v>
       </c>
-      <c r="G24" s="43">
+      <c r="G26" s="43">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B27" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C27" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="12">
+      <c r="D27" s="10"/>
+      <c r="E27" s="12">
         <v>1</v>
       </c>
-      <c r="F25" s="40">
+      <c r="F27" s="40">
         <v>199</v>
       </c>
-      <c r="G25" s="43">
+      <c r="G27" s="43">
         <f t="shared" si="0"/>
         <v>199</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="12">
-        <v>5</v>
-      </c>
-      <c r="F26" s="40">
-        <v>897</v>
-      </c>
-      <c r="G26" s="43">
-        <f>E26*F26</f>
-        <v>4485</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>160</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="12">
-        <v>4</v>
-      </c>
-      <c r="F27" s="40">
-        <v>49</v>
-      </c>
-      <c r="G27" s="43">
-        <f t="shared" ref="G27" si="6">E27*F27</f>
-        <v>196</v>
-      </c>
-    </row>
     <row r="28" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="10" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C28" s="41" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D28" s="10"/>
       <c r="E28" s="12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F28" s="40">
-        <v>377</v>
+        <v>49</v>
       </c>
       <c r="G28" s="43">
-        <f>E28*F28</f>
-        <v>377</v>
+        <f t="shared" ref="G28" si="6">E28*F28</f>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C29" s="41" t="s">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="12">
         <v>1</v>
       </c>
       <c r="F29" s="40">
-        <v>1999</v>
+        <v>377</v>
       </c>
       <c r="G29" s="43">
         <f>E29*F29</f>
-        <v>1999</v>
+        <v>377</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="12">
         <v>1</v>
       </c>
       <c r="F30" s="40">
-        <v>600</v>
+        <v>1999</v>
       </c>
       <c r="G30" s="43">
         <f>E30*F30</f>
-        <v>600</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="12">
         <v>1</v>
       </c>
       <c r="F31" s="40">
-        <v>265</v>
+        <v>600</v>
       </c>
       <c r="G31" s="43">
         <f>E31*F31</f>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="10"/>
+      <c r="E32" s="12">
+        <v>1</v>
+      </c>
+      <c r="F32" s="40">
         <v>265</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="52" t="s">
+      <c r="G32" s="43">
+        <f>E32*F32</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="54"/>
-    </row>
-    <row r="33" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="12">
-        <v>50</v>
-      </c>
-      <c r="F33" s="40">
-        <v>0.3</v>
-      </c>
-      <c r="G33" s="43">
-        <f t="shared" ref="G33:G36" si="7">E33*F33</f>
-        <v>15</v>
-      </c>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="52"/>
     </row>
     <row r="34" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>84</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E34" s="12">
         <v>50</v>
@@ -3001,110 +2966,112 @@
         <v>0.3</v>
       </c>
       <c r="G34" s="43">
-        <f t="shared" ref="G34" si="8">E34*F34</f>
+        <f t="shared" ref="G34:G37" si="7">E34*F34</f>
         <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>131</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E35" s="12">
+        <v>50</v>
+      </c>
+      <c r="F35" s="40">
+        <v>0.3</v>
+      </c>
+      <c r="G35" s="43">
+        <f t="shared" ref="G35" si="8">E35*F35</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B36" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C36" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D36" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E35" s="12">
+      <c r="E36" s="12">
         <v>12</v>
       </c>
-      <c r="F35" s="40">
+      <c r="F36" s="40">
         <v>0.36</v>
       </c>
-      <c r="G35" s="43">
+      <c r="G36" s="43">
         <f t="shared" si="7"/>
         <v>4.32</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="12">
-        <v>4</v>
-      </c>
-      <c r="F36" s="40">
-        <v>16.5</v>
-      </c>
-      <c r="G36" s="43">
-        <f t="shared" si="7"/>
-        <v>66</v>
-      </c>
-    </row>
     <row r="37" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="C37" s="41" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="12">
         <v>4</v>
       </c>
       <c r="F37" s="40">
-        <v>49</v>
+        <v>16.5</v>
       </c>
       <c r="G37" s="43">
-        <f t="shared" si="0"/>
-        <v>196</v>
+        <f t="shared" si="7"/>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="10" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="12">
         <v>4</v>
       </c>
       <c r="F38" s="40">
-        <v>897</v>
+        <v>49</v>
       </c>
       <c r="G38" s="43">
-        <f>E38*F38</f>
-        <v>3588</v>
+        <f t="shared" si="0"/>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="52" t="s">
+      <c r="A39" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="54"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="51"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
     </row>
     <row r="40" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="10" t="s">
@@ -3159,7 +3126,7 @@
       <c r="B42" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C42" s="50" t="s">
+      <c r="C42" s="45" t="s">
         <v>188</v>
       </c>
       <c r="D42" s="10" t="s">
@@ -3197,84 +3164,86 @@
       </c>
     </row>
     <row r="44" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="D44" s="46"/>
-      <c r="E44" s="48">
+      <c r="A44" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
+      <c r="E44" s="51"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="52"/>
+    </row>
+    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="12">
         <v>2</v>
       </c>
-      <c r="F44" s="49">
-        <v>897</v>
-      </c>
-      <c r="G44" s="43">
-        <f>E44*F44</f>
-        <v>1794</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="54"/>
+      <c r="F45" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="G45" s="43">
+        <f>E45*F45</f>
+        <v>0.4</v>
+      </c>
     </row>
     <row r="46" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E46" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F46" s="40">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G46" s="43">
-        <f>E46*F46</f>
-        <v>0.4</v>
+        <f t="shared" ref="G46" si="11">E46*F46</f>
+        <v>1.2</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E47" s="12">
         <v>4</v>
       </c>
       <c r="F47" s="40">
-        <v>0.3</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G47" s="43">
-        <f t="shared" ref="G47" si="11">E47*F47</f>
-        <v>1.2</v>
+        <f t="shared" ref="G47" si="12">E47*F47</f>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -3282,109 +3251,109 @@
         <v>89</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E48" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" s="40">
-        <v>0.28000000000000003</v>
+        <v>0.21</v>
       </c>
       <c r="G48" s="43">
-        <f t="shared" ref="G48" si="12">E48*F48</f>
-        <v>1.1200000000000001</v>
+        <f t="shared" ref="G48" si="13">E48*F48</f>
+        <v>0.42</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E49" s="12">
-        <v>2</v>
-      </c>
-      <c r="F49" s="40">
-        <v>0.21</v>
-      </c>
-      <c r="G49" s="43">
-        <f t="shared" ref="G49" si="13">E49*F49</f>
-        <v>0.42</v>
-      </c>
+      <c r="A49" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" s="51"/>
+      <c r="C49" s="51"/>
+      <c r="D49" s="51"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="52"/>
     </row>
     <row r="50" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="B50" s="53"/>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="54"/>
+      <c r="A50" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="12">
+        <v>1</v>
+      </c>
+      <c r="F50" s="40">
+        <v>5</v>
+      </c>
+      <c r="G50" s="43">
+        <f t="shared" ref="G50:G58" si="14">E50*F50</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="51" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="12">
-        <v>1</v>
-      </c>
-      <c r="F51" s="40">
+      <c r="A51" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" s="51"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="52"/>
+    </row>
+    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C52" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="10"/>
+      <c r="E52" s="12">
         <v>5</v>
       </c>
-      <c r="G51" s="43">
-        <f t="shared" ref="G51:G59" si="14">E51*F51</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="B52" s="53"/>
-      <c r="C52" s="53"/>
-      <c r="D52" s="53"/>
-      <c r="E52" s="53"/>
-      <c r="F52" s="53"/>
-      <c r="G52" s="54"/>
+      <c r="F52" s="40">
+        <v>13.19</v>
+      </c>
+      <c r="G52" s="43">
+        <f t="shared" si="14"/>
+        <v>65.95</v>
+      </c>
     </row>
     <row r="53" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C53" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="D53" s="10"/>
+        <v>181</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>182</v>
+      </c>
       <c r="E53" s="12">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F53" s="40">
-        <v>13.19</v>
+        <v>0.95</v>
       </c>
       <c r="G53" s="43">
         <f t="shared" si="14"/>
-        <v>65.95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -3392,36 +3361,30 @@
         <v>179</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="C54" s="41" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>182</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
       <c r="E54" s="12">
-        <v>20</v>
-      </c>
-      <c r="F54" s="40">
-        <v>0.95</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="F54" s="40"/>
       <c r="G54" s="43">
         <f t="shared" si="14"/>
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="10"/>
       <c r="E55" s="12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F55" s="40"/>
       <c r="G55" s="43">
@@ -3431,11 +3394,9 @@
     </row>
     <row r="56" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>193</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="B56" s="10"/>
       <c r="C56" s="10"/>
       <c r="D56" s="10"/>
       <c r="E56" s="12">
@@ -3448,15 +3409,11 @@
       </c>
     </row>
     <row r="57" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>194</v>
-      </c>
+      <c r="A57" s="10"/>
       <c r="B57" s="10"/>
       <c r="C57" s="10"/>
       <c r="D57" s="10"/>
-      <c r="E57" s="12">
-        <v>8</v>
-      </c>
+      <c r="E57" s="12"/>
       <c r="F57" s="40"/>
       <c r="G57" s="43">
         <f t="shared" si="14"/>
@@ -3476,79 +3433,66 @@
       </c>
     </row>
     <row r="59" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="10"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="43">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G60" s="44">
-        <f>SUM(G3:G59)</f>
-        <v>13997.604000000003</v>
+      <c r="G59" s="44">
+        <f>SUM(G3:G58)</f>
+        <v>10180.604000000003</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A52:G52"/>
+  <mergeCells count="7">
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A49:G49"/>
   </mergeCells>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="12" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{A478C749-2080-B344-A289-CDF5D97B29A2}"/>
-    <hyperlink ref="C3" r:id="rId2" xr:uid="{B2AA866E-24F3-1646-ACED-D65EF9988155}"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{A478C749-2080-B344-A289-CDF5D97B29A2}"/>
+    <hyperlink ref="C5" r:id="rId2" xr:uid="{B2AA866E-24F3-1646-ACED-D65EF9988155}"/>
     <hyperlink ref="C40" r:id="rId3" xr:uid="{5010F871-A4EB-C348-B9FA-9AFAB7A4795F}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{6D0F970B-33A6-5741-B59A-13BE191765B5}"/>
-    <hyperlink ref="C46" r:id="rId5" xr:uid="{6E9AF94B-6606-EF47-BF3F-E19A5CFAFBEA}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{D08990E8-0BCD-A44E-8FA8-5BE704D9FBEC}"/>
-    <hyperlink ref="C9" r:id="rId7" xr:uid="{E2E6BF14-5F83-F745-A590-905519EB4A90}"/>
-    <hyperlink ref="C10" r:id="rId8" xr:uid="{53620724-76B4-204B-AE5B-48ED373D3F0E}"/>
-    <hyperlink ref="C11" r:id="rId9" xr:uid="{3751F033-84A3-2049-9763-EEFF4D133951}"/>
-    <hyperlink ref="C13" r:id="rId10" xr:uid="{5C479939-3F8D-3446-86C5-81A48446719D}"/>
-    <hyperlink ref="C17" r:id="rId11" xr:uid="{47964371-1F96-6147-B384-4A7FCC0FB339}"/>
-    <hyperlink ref="C19" r:id="rId12" xr:uid="{0D761B1C-BFCE-CA4C-AC56-8959BBCD1D8C}"/>
-    <hyperlink ref="C14" r:id="rId13" xr:uid="{C2BA66AB-51D1-4E48-BDF6-5786EE1F2757}"/>
-    <hyperlink ref="C12" r:id="rId14" xr:uid="{5A619F16-5DF6-7A47-930C-607E13BD2744}"/>
-    <hyperlink ref="C20" r:id="rId15" xr:uid="{63E6DFF5-E6E6-9D48-BEF0-976C1610D4CA}"/>
-    <hyperlink ref="C18" r:id="rId16" xr:uid="{33FB920F-0669-0043-8C0C-BC6FBFCB38E1}"/>
-    <hyperlink ref="C15" r:id="rId17" xr:uid="{E3D98391-497D-E645-A06E-B9C450FAA734}"/>
-    <hyperlink ref="C16" r:id="rId18" xr:uid="{A82B3F0C-F6F0-BA48-95E6-EDBA66CD97B8}"/>
-    <hyperlink ref="C33" r:id="rId19" xr:uid="{D95FFA29-399D-6745-AC54-EDBAF115DD55}"/>
-    <hyperlink ref="C35" r:id="rId20" xr:uid="{DE78C3B5-25F3-B54C-AF32-A45A3CCF82C6}"/>
-    <hyperlink ref="C25" r:id="rId21" xr:uid="{E5990545-4A5C-BF4D-A2E3-33113701B5BE}"/>
-    <hyperlink ref="C26" r:id="rId22" xr:uid="{D97E6BC1-9B0F-7E4B-8DD8-6831F4863D0B}"/>
-    <hyperlink ref="C38" r:id="rId23" xr:uid="{52B47181-A334-734F-89EA-4D3CC6EE8FEE}"/>
-    <hyperlink ref="C44" r:id="rId24" xr:uid="{9DED03EC-6FA0-E340-9F64-4A2AFDB1BB32}"/>
-    <hyperlink ref="C34" r:id="rId25" xr:uid="{1B940CD5-6B42-114A-91F4-C00313929BF7}"/>
-    <hyperlink ref="C36" r:id="rId26" xr:uid="{9BF33B54-D294-6A41-BBDB-50238FA80D2D}"/>
-    <hyperlink ref="C42" r:id="rId27" display="https://item.taobao.com/item.htm?id=537967383377&amp;skuId=5461813862733" xr:uid="{F14BE297-86D6-B04A-98BE-ECD2D9A15FD8}"/>
-    <hyperlink ref="C21" r:id="rId28" xr:uid="{A0566B4B-F7CD-C14A-9EBE-943CA43F653D}"/>
-    <hyperlink ref="C22" r:id="rId29" xr:uid="{4BBCC18B-64B9-3948-8B17-249473C5AF6C}"/>
-    <hyperlink ref="C48" r:id="rId30" xr:uid="{AFDE7C59-FB6E-0B4D-A90B-C615F01A2424}"/>
-    <hyperlink ref="C47" r:id="rId31" xr:uid="{7295D0B3-C7AB-5D42-9A78-48C8E9745CA1}"/>
-    <hyperlink ref="C49" r:id="rId32" xr:uid="{0CFFB14A-47E8-B945-BCEB-B671BA1D6F52}"/>
-    <hyperlink ref="C28" r:id="rId33" xr:uid="{6A187383-C123-564D-BC92-969FA3FB5726}"/>
-    <hyperlink ref="C24" r:id="rId34" xr:uid="{1A29D440-BF31-E94C-BCA6-0C1202A21991}"/>
-    <hyperlink ref="C29" r:id="rId35" xr:uid="{36344359-AB27-274E-A2FC-98CD85B6FB8C}"/>
-    <hyperlink ref="C30" r:id="rId36" xr:uid="{A971E1C7-2D55-DA4F-9835-BC42C1DB56AF}"/>
-    <hyperlink ref="C37" r:id="rId37" xr:uid="{902445E2-BD52-B240-B54D-20CF95DAB079}"/>
-    <hyperlink ref="C27" r:id="rId38" xr:uid="{D0310BD2-7368-3C4A-AB34-40C7279D4F0B}"/>
-    <hyperlink ref="C31" r:id="rId39" xr:uid="{FAD92DE1-A270-F24C-8E9F-F880408C8288}"/>
-    <hyperlink ref="C23" r:id="rId40" xr:uid="{3E7B7CBC-84DD-1241-A9BD-85A9EBC5992B}"/>
-    <hyperlink ref="C53" r:id="rId41" xr:uid="{164D90D5-3E91-3245-93D1-4C111CB2C8F2}"/>
-    <hyperlink ref="C54" r:id="rId42" xr:uid="{0925B719-C096-EE4D-83FA-1C819A974518}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{6D0F970B-33A6-5741-B59A-13BE191765B5}"/>
+    <hyperlink ref="C45" r:id="rId5" xr:uid="{6E9AF94B-6606-EF47-BF3F-E19A5CFAFBEA}"/>
+    <hyperlink ref="C9" r:id="rId6" xr:uid="{D08990E8-0BCD-A44E-8FA8-5BE704D9FBEC}"/>
+    <hyperlink ref="C11" r:id="rId7" xr:uid="{E2E6BF14-5F83-F745-A590-905519EB4A90}"/>
+    <hyperlink ref="C12" r:id="rId8" xr:uid="{53620724-76B4-204B-AE5B-48ED373D3F0E}"/>
+    <hyperlink ref="C13" r:id="rId9" xr:uid="{3751F033-84A3-2049-9763-EEFF4D133951}"/>
+    <hyperlink ref="C15" r:id="rId10" xr:uid="{5C479939-3F8D-3446-86C5-81A48446719D}"/>
+    <hyperlink ref="C19" r:id="rId11" xr:uid="{47964371-1F96-6147-B384-4A7FCC0FB339}"/>
+    <hyperlink ref="C21" r:id="rId12" xr:uid="{0D761B1C-BFCE-CA4C-AC56-8959BBCD1D8C}"/>
+    <hyperlink ref="C16" r:id="rId13" xr:uid="{C2BA66AB-51D1-4E48-BDF6-5786EE1F2757}"/>
+    <hyperlink ref="C14" r:id="rId14" xr:uid="{5A619F16-5DF6-7A47-930C-607E13BD2744}"/>
+    <hyperlink ref="C22" r:id="rId15" xr:uid="{63E6DFF5-E6E6-9D48-BEF0-976C1610D4CA}"/>
+    <hyperlink ref="C20" r:id="rId16" xr:uid="{33FB920F-0669-0043-8C0C-BC6FBFCB38E1}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{E3D98391-497D-E645-A06E-B9C450FAA734}"/>
+    <hyperlink ref="C18" r:id="rId18" xr:uid="{A82B3F0C-F6F0-BA48-95E6-EDBA66CD97B8}"/>
+    <hyperlink ref="C34" r:id="rId19" xr:uid="{D95FFA29-399D-6745-AC54-EDBAF115DD55}"/>
+    <hyperlink ref="C36" r:id="rId20" xr:uid="{DE78C3B5-25F3-B54C-AF32-A45A3CCF82C6}"/>
+    <hyperlink ref="C27" r:id="rId21" xr:uid="{E5990545-4A5C-BF4D-A2E3-33113701B5BE}"/>
+    <hyperlink ref="C35" r:id="rId22" xr:uid="{1B940CD5-6B42-114A-91F4-C00313929BF7}"/>
+    <hyperlink ref="C37" r:id="rId23" xr:uid="{9BF33B54-D294-6A41-BBDB-50238FA80D2D}"/>
+    <hyperlink ref="C42" r:id="rId24" display="https://item.taobao.com/item.htm?id=537967383377&amp;skuId=5461813862733" xr:uid="{F14BE297-86D6-B04A-98BE-ECD2D9A15FD8}"/>
+    <hyperlink ref="C23" r:id="rId25" xr:uid="{A0566B4B-F7CD-C14A-9EBE-943CA43F653D}"/>
+    <hyperlink ref="C24" r:id="rId26" xr:uid="{4BBCC18B-64B9-3948-8B17-249473C5AF6C}"/>
+    <hyperlink ref="C47" r:id="rId27" xr:uid="{AFDE7C59-FB6E-0B4D-A90B-C615F01A2424}"/>
+    <hyperlink ref="C46" r:id="rId28" xr:uid="{7295D0B3-C7AB-5D42-9A78-48C8E9745CA1}"/>
+    <hyperlink ref="C48" r:id="rId29" xr:uid="{0CFFB14A-47E8-B945-BCEB-B671BA1D6F52}"/>
+    <hyperlink ref="C29" r:id="rId30" xr:uid="{6A187383-C123-564D-BC92-969FA3FB5726}"/>
+    <hyperlink ref="C26" r:id="rId31" xr:uid="{1A29D440-BF31-E94C-BCA6-0C1202A21991}"/>
+    <hyperlink ref="C30" r:id="rId32" xr:uid="{36344359-AB27-274E-A2FC-98CD85B6FB8C}"/>
+    <hyperlink ref="C31" r:id="rId33" xr:uid="{A971E1C7-2D55-DA4F-9835-BC42C1DB56AF}"/>
+    <hyperlink ref="C38" r:id="rId34" xr:uid="{902445E2-BD52-B240-B54D-20CF95DAB079}"/>
+    <hyperlink ref="C28" r:id="rId35" xr:uid="{D0310BD2-7368-3C4A-AB34-40C7279D4F0B}"/>
+    <hyperlink ref="C32" r:id="rId36" xr:uid="{FAD92DE1-A270-F24C-8E9F-F880408C8288}"/>
+    <hyperlink ref="C25" r:id="rId37" xr:uid="{3E7B7CBC-84DD-1241-A9BD-85A9EBC5992B}"/>
+    <hyperlink ref="C52" r:id="rId38" xr:uid="{164D90D5-3E91-3245-93D1-4C111CB2C8F2}"/>
+    <hyperlink ref="C53" r:id="rId39" xr:uid="{0925B719-C096-EE4D-83FA-1C819A974518}"/>
+    <hyperlink ref="C3" r:id="rId40" xr:uid="{C99824F5-086E-4749-9FA8-DC98BD0BBC70}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId43"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId41"/>
 </worksheet>
 </file>
 
@@ -3557,26 +3501,26 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="23.5" style="55" customWidth="1"/>
-    <col min="3" max="3" width="24" style="55" customWidth="1"/>
+    <col min="1" max="2" width="23.5" style="47" customWidth="1"/>
+    <col min="3" max="3" width="24" style="47" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="52.83203125" style="57" customWidth="1"/>
+    <col min="5" max="5" width="52.83203125" style="49" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="46" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="51" t="s">
+      <c r="D1" s="46" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="48" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3598,19 +3542,19 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="47" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="47" t="s">
         <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E3" s="57" t="s">
+      <c r="E3" s="49" t="s">
         <v>209</v>
       </c>
     </row>
